--- a/outputs/22-47.xlsx
+++ b/outputs/22-47.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">HUSSNI</t>
   </si>
   <si>
+    <t xml:space="preserve">HAMAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOHSION</t>
+  </si>
+  <si>
     <t xml:space="preserve">HAMMED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAMAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOHSION</t>
   </si>
   <si>
     <t xml:space="preserve">HASSNA</t>
@@ -186,28 +186,32 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -466,339 +470,339 @@
   <dimension ref="A1:J195"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="3"/>
+      <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>123344555</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="F2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="D2" s="3"/>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>133444422</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>123688888</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="F3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>123444441</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>145698888</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="F4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>133444424</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>133444441</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="F5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>123344577</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>133444422</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="F6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>123344555</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="F7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>123688888</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>123688888</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="F3" s="4" t="n">
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>145698888</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>123444441</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>133444441</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>123344577</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>133444423</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>133444425</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>123344577</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>133444422</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>133444423</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="4" t="n">
-        <v>123344577</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>145698888</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="F4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="4" t="n">
+      <c r="C18" s="5" t="n">
+        <v>133444424</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>133444425</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="5" t="n">
         <v>123444441</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>133444441</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="F5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>123688888</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>133444422</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="F6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>133444422</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="F7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>133444423</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>133444424</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>123444441</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>133444425</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>123344577</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>133444441</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>145698888</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>123344577</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>133444422</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>133444423</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>133444424</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>133444425</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>123444441</v>
-      </c>
     </row>
     <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G194" s="0" t="s">
+      <c r="G194" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G195" s="0" t="s">
+      <c r="G195" s="1" t="s">
         <v>13</v>
       </c>
     </row>
@@ -821,62 +825,62 @@
   <dimension ref="B1:B11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
